--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80855842</v>
+        <v>80855836</v>
       </c>
       <c r="B2" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702811.7922784629</v>
+        <v>702863</v>
       </c>
       <c r="R2" t="n">
-        <v>6650287.220193557</v>
+        <v>6650255</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +746,14 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga i kanten mot tallmosse.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,16 +784,11 @@
         <v>80855839</v>
       </c>
       <c r="B3" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -850,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702816.0514408005</v>
+        <v>702816</v>
       </c>
       <c r="R3" t="n">
-        <v>6650282.934946435</v>
+        <v>6650283</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,19 +860,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80855909</v>
+        <v>80855850</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,25 +901,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>4189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -966,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702670.0976802955</v>
+        <v>702810</v>
       </c>
       <c r="R4" t="n">
-        <v>6650312.079358582</v>
+        <v>6650293</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,19 +969,14 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,43 +1004,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80855845</v>
+        <v>80855842</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702804.1669417064</v>
+        <v>702812</v>
       </c>
       <c r="R5" t="n">
-        <v>6650297.848230576</v>
+        <v>6650287</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,19 +1083,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,12 +1116,7 @@
         <v>80855853</v>
       </c>
       <c r="B6" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702786.0043005884</v>
+        <v>702786</v>
       </c>
       <c r="R6" t="n">
-        <v>6650298.859348726</v>
+        <v>6650299</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,19 +1184,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,15 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80855888</v>
+        <v>80855909</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,33 +1225,25 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1323,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702710.248245741</v>
+        <v>702670</v>
       </c>
       <c r="R7" t="n">
-        <v>6650432.782156887</v>
+        <v>6650312</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,19 +1285,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,42 +1315,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80855850</v>
+        <v>80855888</v>
       </c>
       <c r="B8" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4189</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1447,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702809.9579680657</v>
+        <v>702710</v>
       </c>
       <c r="R8" t="n">
-        <v>6650293.144989151</v>
+        <v>6650433</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1480,24 +1394,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,43 +1424,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80855858</v>
+        <v>80855902</v>
       </c>
       <c r="B9" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1569,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702821.1748253403</v>
+        <v>702914</v>
       </c>
       <c r="R9" t="n">
-        <v>6650317.863054369</v>
+        <v>6650573</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1602,19 +1495,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,15 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80855895</v>
+        <v>80855845</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702840.8455115457</v>
+        <v>702804</v>
       </c>
       <c r="R10" t="n">
-        <v>6650554.934460378</v>
+        <v>6650298</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,19 +1597,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,42 +1627,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80855836</v>
+        <v>80855858</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1802,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702862.860815948</v>
+        <v>702821</v>
       </c>
       <c r="R11" t="n">
-        <v>6650254.875984722</v>
+        <v>6650318</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1835,24 +1699,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På granlåga i kanten mot tallmosse.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,15 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80855902</v>
+        <v>80855895</v>
       </c>
       <c r="B12" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1896,26 +1740,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1923,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702913.7852581796</v>
+        <v>702841</v>
       </c>
       <c r="R12" t="n">
-        <v>6650573.000475702</v>
+        <v>6650555</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1956,19 +1801,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,12 +1834,7 @@
         <v>80855871</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702789.9932083311</v>
+        <v>702790</v>
       </c>
       <c r="R13" t="n">
-        <v>6650381.928289496</v>
+        <v>6650382</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2073,19 +1903,9 @@
           <t>2019-11-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855836</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855842</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855853</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855909</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855888</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1522,6 +1562,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855902</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855845</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855858</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855895</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,8 +1990,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855871</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,56 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80855839</v>
+        <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>93205</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2058</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702816</v>
+        <v>702690</v>
       </c>
       <c r="R3" t="n">
-        <v>6650283</v>
+        <v>6650348</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,12 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,80 +880,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855839</t>
+          <t>https://artportalen.se/Sighting/135958212</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80855850</v>
+        <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>91330</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702810</v>
+        <v>702737</v>
       </c>
       <c r="R4" t="n">
-        <v>6650293</v>
+        <v>6650467</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,17 +968,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I barrmatta under gammal gran.</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,34 +992,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855850</t>
+          <t>https://artportalen.se/Sighting/135958213</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80855842</v>
+        <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>93189</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,45 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702812</v>
+        <v>702897</v>
       </c>
       <c r="R5" t="n">
-        <v>6650287</v>
+        <v>6650271</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,12 +1080,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,72 +1104,68 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855842</t>
+          <t>https://artportalen.se/Sighting/135958244</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80855853</v>
+        <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>93215</v>
+        <v>92723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4368</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702786</v>
+        <v>702770</v>
       </c>
       <c r="R6" t="n">
-        <v>6650299</v>
+        <v>6650559</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1206,12 +1192,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,34 +1216,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855853</t>
+          <t>https://artportalen.se/Sighting/135958215</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80855909</v>
+        <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1250,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702670</v>
+        <v>702759</v>
       </c>
       <c r="R7" t="n">
-        <v>6650312</v>
+        <v>6650463</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,12 +1304,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,56 +1328,55 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855909</t>
+          <t>https://artportalen.se/Sighting/135958233</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80855888</v>
+        <v>80855839</v>
       </c>
       <c r="B8" t="n">
-        <v>93233</v>
+        <v>93205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>2058</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1396,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702710</v>
+        <v>702816</v>
       </c>
       <c r="R8" t="n">
-        <v>6650433</v>
+        <v>6650283</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,54 +1459,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855888</t>
+          <t>https://artportalen.se/Sighting/80855839</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80855902</v>
+        <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>93233</v>
+        <v>96488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702914</v>
+        <v>702738</v>
       </c>
       <c r="R9" t="n">
-        <v>6650573</v>
+        <v>6650315</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,12 +1530,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,34 +1554,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855902</t>
+          <t>https://artportalen.se/Sighting/135958199</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80855845</v>
+        <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>106244</v>
+        <v>96488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,38 +1588,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702804</v>
+        <v>702694</v>
       </c>
       <c r="R10" t="n">
-        <v>6650298</v>
+        <v>6650341</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1639,12 +1642,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,34 +1666,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855845</t>
+          <t>https://artportalen.se/Sighting/135958208</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80855858</v>
+        <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>106244</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,38 +1700,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702821</v>
+        <v>702844</v>
       </c>
       <c r="R11" t="n">
-        <v>6650318</v>
+        <v>6650565</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,12 +1754,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,34 +1778,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855858</t>
+          <t>https://artportalen.se/Sighting/135958219</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80855895</v>
+        <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>106244</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1795,38 +1812,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702841</v>
+        <v>702791</v>
       </c>
       <c r="R12" t="n">
-        <v>6650555</v>
+        <v>6650389</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1853,12 +1866,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,34 +1890,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80855895</t>
+          <t>https://artportalen.se/Sighting/135958239</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80855871</v>
+        <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>101326</v>
+        <v>96488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,38 +1924,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogshult, N om, Upl</t>
+          <t>Skogshult, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702790</v>
+        <v>702878</v>
       </c>
       <c r="R13" t="n">
-        <v>6650382</v>
+        <v>6650196</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1960,12 +1978,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,25 +2002,4058 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135958249</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>80855850</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>702810</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6650293</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I barrmatta under gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855850</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135958228</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92446</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>702766</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6650506</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958228</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>80855842</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>702812</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6650287</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855842</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>80855853</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>702786</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6650299</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855853</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>80855909</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>702670</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6650312</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855909</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>80855888</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>702710</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6650433</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>80855902</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>702914</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6650573</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855902</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135958207</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>702684</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6650305</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958207</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135958229</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>702754</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6650509</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958229</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135958250</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>702870</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6650207</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958250</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135958196</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>702744</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6650269</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958196</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135958210</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>702696</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6650341</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958210</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135958248</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4782</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>702886</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6650190</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958248</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135958211</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>702716</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6650349</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958211</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135958216</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>702829</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6650555</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958216</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135958226</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>702794</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6650513</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958226</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135958246</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>702901</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6650251</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958246</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135958227</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>702772</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6650499</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958227</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135958241</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>702806</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6650362</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958241</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135958231</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>702736</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6650508</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958231</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135958232</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>702734</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6650509</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958232</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>80855845</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>702804</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6650298</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855845</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>80855858</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>702821</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6650318</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855858</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>80855895</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>702841</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6650555</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80855895</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135958214</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>702732</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6650512</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958214</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135958234</v>
+      </c>
+      <c r="B39" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>702750</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6650455</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958234</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135958242</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106413</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>702803</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6650332</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958242</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80855871</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skogshult, N om, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>702790</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6650382</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2019-11-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/80855871</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135958198</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>702738</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6650315</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958198</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135958201</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>702732</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6650309</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958201</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135958218</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>702844</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6650565</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958218</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135958224</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>702836</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6650546</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958224</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135958225</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>702833</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6650537</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958225</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135958235</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>702742</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6650450</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958235</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135958238</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skogshult, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>702791</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6650389</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135958238</t>
         </is>
       </c>
     </row>
@@ -2010,6 +6071,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92446</v>
+        <v>92460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>135958207</v>
       </c>
       <c r="B21" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135958229</v>
       </c>
       <c r="B22" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135958250</v>
       </c>
       <c r="B23" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>135958196</v>
       </c>
       <c r="B24" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135958210</v>
       </c>
       <c r="B25" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>135958248</v>
       </c>
       <c r="B26" t="n">
-        <v>4782</v>
+        <v>4783</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135958211</v>
       </c>
       <c r="B27" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135958216</v>
       </c>
       <c r="B28" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>135958226</v>
       </c>
       <c r="B29" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135958246</v>
       </c>
       <c r="B30" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135958227</v>
       </c>
       <c r="B31" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135958241</v>
       </c>
       <c r="B32" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92738</v>
+        <v>92739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92738</v>
+        <v>92739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92739</v>
+        <v>92740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92739</v>
+        <v>92740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92462</v>
+        <v>92463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>135958207</v>
       </c>
       <c r="B21" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135958229</v>
       </c>
       <c r="B22" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135958250</v>
       </c>
       <c r="B23" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135958211</v>
       </c>
       <c r="B27" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135958216</v>
       </c>
       <c r="B28" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>135958226</v>
       </c>
       <c r="B29" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135958246</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135958227</v>
       </c>
       <c r="B31" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92463</v>
+        <v>92469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>135958207</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135958229</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135958250</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135958211</v>
       </c>
       <c r="B27" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135958216</v>
       </c>
       <c r="B28" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>135958226</v>
       </c>
       <c r="B29" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135958246</v>
       </c>
       <c r="B30" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135958227</v>
       </c>
       <c r="B31" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92747</v>
+        <v>92748</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92747</v>
+        <v>92748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92469</v>
+        <v>92470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>135958207</v>
       </c>
       <c r="B21" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135958229</v>
       </c>
       <c r="B22" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135958250</v>
       </c>
       <c r="B23" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135958211</v>
       </c>
       <c r="B27" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135958216</v>
       </c>
       <c r="B28" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>135958226</v>
       </c>
       <c r="B29" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135958246</v>
       </c>
       <c r="B30" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135958227</v>
       </c>
       <c r="B31" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92470</v>
+        <v>92476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92476</v>
+        <v>92483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>135958207</v>
       </c>
       <c r="B21" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135958229</v>
       </c>
       <c r="B22" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135958250</v>
       </c>
       <c r="B23" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135958211</v>
       </c>
       <c r="B27" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135958216</v>
       </c>
       <c r="B28" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>135958226</v>
       </c>
       <c r="B29" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135958246</v>
       </c>
       <c r="B30" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135958227</v>
       </c>
       <c r="B31" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92761</v>
+        <v>92762</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92761</v>
+        <v>92762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92483</v>
+        <v>92484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92762</v>
+        <v>92775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92762</v>
+        <v>92775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92484</v>
+        <v>92497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>135958207</v>
       </c>
       <c r="B21" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135958229</v>
       </c>
       <c r="B22" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135958250</v>
       </c>
       <c r="B23" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>135958211</v>
       </c>
       <c r="B27" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>135958216</v>
       </c>
       <c r="B28" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>135958226</v>
       </c>
       <c r="B29" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135958246</v>
       </c>
       <c r="B30" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>135958227</v>
       </c>
       <c r="B31" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 26081-2026 artfynd.xlsx
+++ b/artfynd/A 26081-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>135958212</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>135958213</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>135958244</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135958215</v>
       </c>
       <c r="B6" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135958233</v>
       </c>
       <c r="B7" t="n">
-        <v>92775</v>
+        <v>92776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>135958199</v>
       </c>
       <c r="B9" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>135958208</v>
       </c>
       <c r="B10" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135958219</v>
       </c>
       <c r="B11" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>135958239</v>
       </c>
       <c r="B12" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135958249</v>
       </c>
       <c r="B13" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>135958228</v>
       </c>
       <c r="B15" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135958231</v>
       </c>
       <c r="B33" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135958232</v>
       </c>
       <c r="B34" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>135958214</v>
       </c>
       <c r="B38" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>135958234</v>
       </c>
       <c r="B39" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>135958242</v>
       </c>
       <c r="B40" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>135958198</v>
       </c>
       <c r="B42" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>135958201</v>
       </c>
       <c r="B43" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>135958218</v>
       </c>
       <c r="B44" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>135958224</v>
       </c>
       <c r="B45" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>135958225</v>
       </c>
       <c r="B46" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135958235</v>
       </c>
       <c r="B47" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>135958238</v>
       </c>
       <c r="B48" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
